--- a/docs/05_ECONOMIA_UNITARIA.xlsx
+++ b/docs/05_ECONOMIA_UNITARIA.xlsx
@@ -11,7 +11,10 @@
     <sheet name="Leyenda" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Supuestos" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Escenarios" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sensibilidad" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Test de precio" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Capital circulante" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Panel semanal" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Sensibilidad" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,45 +26,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
-  <si>
-    <t xml:space="preserve">Economía unitaria · Prototipo «Descanso Compartido»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha: 13/10/2026 · Estado: NO-GO. Ninguna cifra de este libro es un coste real ni una previsión de beneficio.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
+  <si>
+    <t xml:space="preserve">Economía unitaria · Descanso Compartido · V2 (13/10/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninguna cifra de este libro es un coste o precio real confirmado salvo lo que el titular escriba en la columna REAL con facturas o cotizaciones firmadas.</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo usarlo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Celdas con fondo AMARILLO y texto AZUL = datos que debéis rellenar o cambiar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Texto NEGRO = fórmulas. No las sobrescribáis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Columna «REAL» de la hoja Escenarios: vacía a propósito. Rellenadla SOLO con cotizaciones firmadas (DP-07).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Los escenarios 1–5 reproducen los ejemplos HIPOTÉTICOS de los informes (Estudio §9.2 y Maestro §09).</t>
+    <t xml:space="preserve">1. Celdas AMARILLAS con texto AZUL = datos editables. Texto NEGRO = fórmulas (no sobrescribir). VERDE = enlace a otra hoja.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Columna REAL (hoja Escenarios): rellenar las 5 partidas del coste (filas 7–11). Si falta UNA, la columna muestra «DATOS INCOMPLETOS» y no calcula margen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Una partida que realmente vale 0 se escribe 0; una celda VACÍA significa «no lo sé» y bloquea el cálculo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Escenarios 1–5 = hipótesis de los informes (coste agregado). Reproducen 0,56 / 7,04 / 11,54 / 11,03 / 7,14 €.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Veredictos posibles: «Supera umbral (hipótesis)», «No supera (hipótesis)», «Supera umbral», «No supera», «DATOS INCOMPLETOS». Nunca «rentable».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formato esperado de una fila del panel semanal (ejemplo de FORMATO, no son datos): semana 2026-W43 · sesiones 1.000 · sesiones con vista de producto 400 · con ATC 40 · con checkout 20 · pedidos 10 · ventas brutas 299,00 € …</t>
   </si>
   <si>
     <t xml:space="preserve">Fuentes de los supuestos</t>
   </si>
   <si>
-    <t xml:space="preserve">IVA 21 %: tipo general (Agencia Tributaria, S25). El tipo aplicable al SKU está SIN CONFIRMAR (DP-22).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión 2,9 % + 0,30 €: supuesto prudencial de los informes, NO tarifa contractual de Shopify (S26).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva de incidencias y umbral de 7–8 €: criterio analítico del Estudio §9.2, no datos observados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital 50 €: presupuesto declarado por el titular.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excluido: cuota Shopify, apps, gestoría, IRPF, devoluciones extraordinarias, publicidad, deducibilidad del IVA soportado.</t>
+    <t xml:space="preserve">IVA 21 %: tipo general (AEAT, S25); tipo del SKU pendiente de confirmar por asesoría.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión 2,9 % + 0,30 €: supuesto prudencial de los informes; sustituir por la tarifa real del plan (fila «Comisión real»).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidación Shopify Payments ≥ 3 días hábiles (S27). Capital 50 €: presupuesto declarado por el titular. CAC 10 €: ejemplo del Estudio §9.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No incluido: cuota Shopify, apps, gestoría, IRPF y publicidad salvo CAC.</t>
   </si>
   <si>
     <t xml:space="preserve">Supuestos globales</t>
@@ -79,40 +85,46 @@
     <t xml:space="preserve">IVA aplicado al PVP (hipótesis)</t>
   </si>
   <si>
-    <t xml:space="preserve">S25: tipo general. Tipo del SKU sin clasificar (DP-22).</t>
+    <t xml:space="preserve">S25 tipo general; tipo del SKU pendiente (asesoría).</t>
   </si>
   <si>
     <t xml:space="preserve">Comisión de pago variable (hipótesis)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supuesto de los informes; confirmar tarifa real (DP-11).</t>
+    <t xml:space="preserve">Supuesto de los informes.</t>
   </si>
   <si>
     <t xml:space="preserve">Comisión de pago fija por pedido (hipótesis)</t>
   </si>
   <si>
-    <t xml:space="preserve">Supuesto de los informes.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Umbral mínimo de contribución antes de marketing</t>
   </si>
   <si>
-    <t xml:space="preserve">Estudio §9.2: no avanzar por debajo de 7–8 €.</t>
+    <t xml:space="preserve">Estudio §9.2 (7–8 €).</t>
   </si>
   <si>
     <t xml:space="preserve">Capital disponible para pedidos y reembolsos</t>
   </si>
   <si>
-    <t xml:space="preserve">Presupuesto declarado por el titular.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAC de referencia para comparar (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estudio §9.2: ejemplo de CAC de 10 €.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución por pedido (antes de costes fijos, marketing e impuestos directos)</t>
+    <t xml:space="preserve">Declarado por el titular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC de referencia (hipótesis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudio §9.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días naturales hasta cobrar la liquidación (hipótesis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S27: mínimo 3 días hábiles + banco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución por pedido (antes de costes fijos e impuestos directos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columnas B–F: hipótesis de los informes. Columna G: REAL (solo datos confirmados).</t>
   </si>
   <si>
     <t xml:space="preserve">Concepto</t>
@@ -121,7 +133,7 @@
     <t xml:space="preserve">1. Desfavorable</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Base exploración</t>
+    <t xml:space="preserve">2. Base</t>
   </si>
   <si>
     <t xml:space="preserve">3. Mejor logística</t>
@@ -133,19 +145,31 @@
     <t xml:space="preserve">5. Ejemplo Maestro</t>
   </si>
   <si>
-    <t xml:space="preserve">REAL (cotización firmada)</t>
+    <t xml:space="preserve">REAL (confirmado)</t>
   </si>
   <si>
     <t xml:space="preserve">PVP con IVA</t>
   </si>
   <si>
-    <t xml:space="preserve">Coste completo puesto en cliente (agregado, hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Producto (desglose real)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Envío a domicilio (desglose real)</t>
+    <t xml:space="preserve">Tipo de columna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIPÓTESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste agregado (solo hipótesis; no se admite en REAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · Producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · Envío a domicilio</t>
   </si>
   <si>
     <t xml:space="preserve">  · Aranceles / derecho 3 € / importación</t>
@@ -157,10 +181,25 @@
     <t xml:space="preserve">  · Otros costes variables no recuperables</t>
   </si>
   <si>
+    <t xml:space="preserve">Partidas del desglose rellenadas (de 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado del coste</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coste completo usado</t>
   </si>
   <si>
-    <t xml:space="preserve">Reserva por devoluciones, soporte e incidencias</t>
+    <t xml:space="preserve">Reserva incidencias y soporte por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste esperado de devoluciones por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste de contenido / colaboradores por venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión real % (vacío = usar supuesto)</t>
   </si>
   <si>
     <t xml:space="preserve">PVP sin IVA</t>
@@ -172,31 +211,148 @@
     <t xml:space="preserve">Contribución por pedido</t>
   </si>
   <si>
-    <t xml:space="preserve">¿Supera el umbral mínimo?</t>
+    <t xml:space="preserve">Veredicto frente al umbral</t>
   </si>
   <si>
     <t xml:space="preserve">Contribución tras CAC de referencia</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedidos completos financiables con el capital</t>
+    <t xml:space="preserve">Pedidos financiables con el capital (coste completo)</t>
   </si>
   <si>
     <t xml:space="preserve">Notas</t>
   </si>
   <si>
-    <t xml:space="preserve">Escenarios 1–4: Estudio §9.2 (resultado publicado: 0,56 / 7,04 / 11,54 / 11,03 €). Escenario 5: Maestro §09 (7,14 €). Todos HIPOTÉTICOS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columna REAL: déjala vacía hasta tener cotizaciones firmadas. Si rellenas el desglose (filas 6–10), sustituye al coste agregado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fila 18: con 50 € y un proveedor que cobra al instante, solo se financian 3 pedidos a 14 € (Estudio §9.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilidad de adquisición (hipótesis de planificación, no previsión)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución usada (escenario base, enlazada):</t>
+    <t xml:space="preserve">Fila 13: el fallo de la V1 era IF(SUM(G6:G10)&gt;0,SUM,agregado): con 1 de 5 partidas tomaba ese importe como coste total e inflaba el margen. Ahora 1–4 partidas = DATOS INCOMPLETOS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filas 16–17 de las hipótesis valen 0 para reproducir los informes. En REAL deben rellenarse (0 solo si es real).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ningún veredicto dice «rentable»: superar el umbral antes de marketing no implica beneficio (ver fila 23).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test de precio con el mismo coste (hipótesis — no son precios decididos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste usado:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva incidencias:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVP con IVA (a probar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veredicto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tras CAC ref.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital necesario antes de cobrar las liquidaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedidos por día (hipótesis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Editar: escenario de ventas a cubrir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días hasta cobrar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste por pedido pagado al proveedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colchón para reembolsos (pedidos equivalentes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hipótesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital necesario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Suficiente?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedidos/día sostenibles sin capital extra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel semanal (rellenar con datos de Shopify Analytics; sin datos = vacío)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sesiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sesiones con vista de producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sesiones con ATC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sesiones con checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventas brutas (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto de captación (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste de contenido (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devoluciones (nº)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversión tienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATC / vistas producto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkout / ATC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución estimada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa devolución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definiciones: conversión = pedidos/sesiones · ATC = sesiones con añadir al carrito / sesiones con vista de producto · Checkout = sesiones con checkout / sesiones con ATC · AOV = ventas brutas / pedidos · CAC = (captación + contenido) / pedidos. Las visualizaciones en redes NO son sesiones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilidad de adquisición (hipótesis de planificación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución usada:</t>
   </si>
   <si>
     <t xml:space="preserve">Sesiones cualificadas/mes</t>
@@ -211,22 +367,21 @@
     <t xml:space="preserve">Contribución total</t>
   </si>
   <si>
-    <t xml:space="preserve">Capital a adelantar (coste base)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedidos fraccionarios = valor esperado matemático (Estudio §9.5). Las conversiones NO son benchmarks del nicho.</t>
+    <t xml:space="preserve">Capital a adelantar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;;\(#,##0.00&quot; €)&quot;;\-"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="#,##0"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -301,7 +456,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +473,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -355,7 +516,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -376,8 +537,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -388,15 +549,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -408,11 +573,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -420,7 +589,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -433,6 +610,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF4CCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -458,7 +644,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -474,7 +660,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFF4CCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -676,10 +862,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="140"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -721,12 +907,12 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
@@ -734,23 +920,31 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -769,17 +963,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -789,48 +983,48 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>0.21</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0.029</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>0.3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -864,6 +1058,17 @@
       </c>
       <c r="C9" s="4" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -882,16 +1087,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -901,7 +1106,9 @@
       <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -909,32 +1116,32 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="8" t="s">
+    <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="C3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>36</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>24.9</v>
@@ -955,39 +1162,53 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="G5" s="7"/>
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+        <v>44</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -998,7 +1219,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1009,7 +1230,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -1020,7 +1241,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -1030,283 +1251,410 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <f aca="false">IF(SUM(B6:B10)&gt;0,SUM(B6:B10),B5)</f>
-        <v>16</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <f aca="false">IF(SUM(C6:C10)&gt;0,SUM(C6:C10),C5)</f>
-        <v>14</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">IF(SUM(D6:D10)&gt;0,SUM(D6:D10),D5)</f>
-        <v>10</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">IF(SUM(E6:E10)&gt;0,SUM(E6:E10),E5)</f>
-        <v>14</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <f aca="false">IF(SUM(F6:F10)&gt;0,SUM(F6:F10),F5)</f>
-        <v>14.4</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <f aca="false">IF(SUM(G6:G10)&gt;0,SUM(G6:G10),G5)</f>
-        <v>0</v>
-      </c>
+      <c r="A11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B12" s="10" t="n">
+        <f aca="false">COUNT(B7:B11)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <f aca="false">COUNT(C7:C11)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <f aca="false">COUNT(D7:D11)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <f aca="false">COUNT(E7:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <f aca="false">COUNT(F7:F11)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <f aca="false">COUNT(G7:G11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3" t="str">
+        <f aca="false">IF(B12=5,"DESGLOSE COMPLETO",IF(AND(B12=0,B6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
+        <v>HIPÓTESIS (agregado)</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f aca="false">IF(C12=5,"DESGLOSE COMPLETO",IF(AND(C12=0,C6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
+        <v>HIPÓTESIS (agregado)</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f aca="false">IF(D12=5,"DESGLOSE COMPLETO",IF(AND(D12=0,D6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
+        <v>HIPÓTESIS (agregado)</v>
+      </c>
+      <c r="E13" s="3" t="str">
+        <f aca="false">IF(E12=5,"DESGLOSE COMPLETO",IF(AND(E12=0,E6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
+        <v>HIPÓTESIS (agregado)</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f aca="false">IF(F12=5,"DESGLOSE COMPLETO",IF(AND(F12=0,F6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
+        <v>HIPÓTESIS (agregado)</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f aca="false">IF(OR(G4="",G12&lt;5,G15="",G16="",G17=""),"DATOS INCOMPLETOS","COMPLETO")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <f aca="false">IF(B13="DATOS INCOMPLETOS","—",IF(B12=5,SUM(B7:B11),B6))</f>
+        <v>16</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <f aca="false">IF(C13="DATOS INCOMPLETOS","—",IF(C12=5,SUM(C7:C11),C6))</f>
+        <v>14</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <f aca="false">IF(D13="DATOS INCOMPLETOS","—",IF(D12=5,SUM(D7:D11),D6))</f>
+        <v>10</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <f aca="false">IF(E13="DATOS INCOMPLETOS","—",IF(E12=5,SUM(E7:E11),E6))</f>
+        <v>14</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <f aca="false">IF(F13="DATOS INCOMPLETOS","—",IF(F12=5,SUM(F7:F11),F6))</f>
+        <v>14.4</v>
+      </c>
+      <c r="G14" s="11" t="str">
+        <f aca="false">IF(G13="DATOS INCOMPLETOS","—",IF(G12=5,SUM(G7:G11),G6))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C15" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E15" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="F12" s="10" t="n">
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">IF(B4="","",B4/(1+Supuestos!$B$4))</f>
-        <v>20.5785123966942</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <f aca="false">IF(C4="","",C4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">IF(D4="","",D4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">IF(E4="","",E4/(1+Supuestos!$B$4))</f>
-        <v>28.8429752066116</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <f aca="false">IF(F4="","",F4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="G13" s="9" t="str">
-        <f aca="false">IF(G4="","",G4/(1+Supuestos!$B$4))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">IF(B4="","",B4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v>1.0221</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <f aca="false">IF(C4="","",C4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">IF(D4="","",D4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <f aca="false">IF(E4="","",E4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v>1.3121</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <f aca="false">IF(F4="","",F4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="G14" s="9" t="str">
-        <f aca="false">IF(G4="","",G4*Supuestos!$B$5+Supuestos!$B$6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <f aca="false">IF(B4="","",B13-B11-B12-B14)</f>
-        <v>0.556412396694215</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <f aca="false">IF(C4="","",C13-C11-C12-C14)</f>
-        <v>7.04364380165289</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <f aca="false">IF(D4="","",D13-D11-D12-D14)</f>
-        <v>11.5436438016529</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <f aca="false">IF(E4="","",E13-E11-E12-E14)</f>
-        <v>11.0308752066116</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <f aca="false">IF(F4="","",F13-F11-F12-F14)</f>
-        <v>7.14364380165289</v>
-      </c>
-      <c r="G15" s="11" t="str">
-        <f aca="false">IF(G4="","",G13-G11-G12-G14)</f>
-        <v/>
-      </c>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4" t="str">
-        <f aca="false">IF(B4="","Sin datos",IF(B15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>NO</v>
-      </c>
-      <c r="C16" s="4" t="str">
-        <f aca="false">IF(C4="","Sin datos",IF(C15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>Sí</v>
-      </c>
-      <c r="D16" s="4" t="str">
-        <f aca="false">IF(D4="","Sin datos",IF(D15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>Sí</v>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f aca="false">IF(E4="","Sin datos",IF(E15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>Sí</v>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f aca="false">IF(F4="","Sin datos",IF(F15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>Sí</v>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f aca="false">IF(G4="","Sin datos",IF(G15&gt;=Supuestos!$B$7,"Sí","NO"))</f>
-        <v>Sin datos</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="9" t="n">
-        <f aca="false">IF(B4="","",B15-Supuestos!$B$9)</f>
-        <v>-9.44358760330579</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <f aca="false">IF(C4="","",C15-Supuestos!$B$9)</f>
-        <v>-2.95635619834711</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">IF(D4="","",D15-Supuestos!$B$9)</f>
-        <v>1.54364380165289</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <f aca="false">IF(E4="","",E15-Supuestos!$B$9)</f>
-        <v>1.03087520661157</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <f aca="false">IF(F4="","",F15-Supuestos!$B$9)</f>
-        <v>-2.85635619834711</v>
-      </c>
-      <c r="G17" s="9" t="str">
-        <f aca="false">IF(G4="","",G15-Supuestos!$B$9)</f>
-        <v/>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <f aca="false">IF(B11&gt;0,INT(Supuestos!$B$8/B11),"Sin datos")</f>
+        <v>57</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="11" t="n">
+        <f aca="false">IF(B4="","—",B4/(1+Supuestos!$B$4))</f>
+        <v>20.5785123966942</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <f aca="false">IF(C4="","—",C4/(1+Supuestos!$B$4))</f>
+        <v>24.7107438016529</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <f aca="false">IF(D4="","—",D4/(1+Supuestos!$B$4))</f>
+        <v>24.7107438016529</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <f aca="false">IF(E4="","—",E4/(1+Supuestos!$B$4))</f>
+        <v>28.8429752066116</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <f aca="false">IF(F4="","—",F4/(1+Supuestos!$B$4))</f>
+        <v>24.7107438016529</v>
+      </c>
+      <c r="G19" s="11" t="str">
+        <f aca="false">IF(G4="","—",G4/(1+Supuestos!$B$4))</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="11" t="n">
+        <f aca="false">IF(B4="","—",B4*IF(B18="",Supuestos!$B$5,B18)+Supuestos!$B$6)</f>
+        <v>1.0221</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <f aca="false">IF(C4="","—",C4*IF(C18="",Supuestos!$B$5,C18)+Supuestos!$B$6)</f>
+        <v>1.1671</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <f aca="false">IF(D4="","—",D4*IF(D18="",Supuestos!$B$5,D18)+Supuestos!$B$6)</f>
+        <v>1.1671</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <f aca="false">IF(E4="","—",E4*IF(E18="",Supuestos!$B$5,E18)+Supuestos!$B$6)</f>
+        <v>1.3121</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <f aca="false">IF(F4="","—",F4*IF(F18="",Supuestos!$B$5,F18)+Supuestos!$B$6)</f>
+        <v>1.1671</v>
+      </c>
+      <c r="G20" s="11" t="str">
+        <f aca="false">IF(G4="","—",G4*IF(G18="",Supuestos!$B$5,G18)+Supuestos!$B$6)</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",B19-B14-B15-B16-B17-B20,"DATOS INCOMPLETOS")</f>
+        <v>0.556412396694215</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",C19-C14-C15-C16-C17-C20,"DATOS INCOMPLETOS")</f>
+        <v>7.04364380165289</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",D19-D14-D15-D16-D17-D20,"DATOS INCOMPLETOS")</f>
+        <v>11.5436438016529</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",E19-E14-E15-E16-E17-E20,"DATOS INCOMPLETOS")</f>
+        <v>11.0308752066116</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",F19-F14-F15-F16-F17-F20,"DATOS INCOMPLETOS")</f>
+        <v>7.14364380165289</v>
+      </c>
+      <c r="G21" s="12" t="str">
+        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",G19-G14-G15-G16-G17-G20,"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="2" t="str">
+        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",IF(B21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
+        <v>No supera (hipótesis)</v>
+      </c>
+      <c r="C22" s="2" t="str">
+        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",IF(C21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",IF(D21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",IF(E21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",IF(F21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="G22" s="2" t="str">
+        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",IF(G21&gt;=Supuestos!$B$7,"Supera umbral","No supera"),"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="11" t="n">
+        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",B21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>-9.44358760330579</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",C21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>-2.95635619834711</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",D21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>1.54364380165289</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",E21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>1.03087520661157</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",F21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>-2.85635619834711</v>
+      </c>
+      <c r="G23" s="11" t="str">
+        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",G21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="10" t="n">
+        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/B14),"DATOS INCOMPLETOS")</f>
         <v>3</v>
       </c>
-      <c r="C18" s="4" t="n">
-        <f aca="false">IF(C11&gt;0,INT(Supuestos!$B$8/C11),"Sin datos")</f>
+      <c r="C24" s="10" t="n">
+        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/C14),"DATOS INCOMPLETOS")</f>
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <f aca="false">IF(D11&gt;0,INT(Supuestos!$B$8/D11),"Sin datos")</f>
+      <c r="D24" s="10" t="n">
+        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/D14),"DATOS INCOMPLETOS")</f>
         <v>5</v>
       </c>
-      <c r="E18" s="4" t="n">
-        <f aca="false">IF(E11&gt;0,INT(Supuestos!$B$8/E11),"Sin datos")</f>
+      <c r="E24" s="10" t="n">
+        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/E14),"DATOS INCOMPLETOS")</f>
         <v>3</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <f aca="false">IF(F11&gt;0,INT(Supuestos!$B$8/F11),"Sin datos")</f>
+      <c r="F24" s="10" t="n">
+        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/F14),"DATOS INCOMPLETOS")</f>
         <v>3</v>
       </c>
-      <c r="G18" s="4" t="str">
-        <f aca="false">IF(G11&gt;0,INT(Supuestos!$B$8/G11),"Sin datos")</f>
-        <v>Sin datos</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G24" s="10" t="str">
+        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/G14),"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B13:G24">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>B13="DATOS INCOMPLETOS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1322,19 +1670,956 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="13" t="n">
+        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G14,Escenarios!C14)</f>
+        <v>14</v>
+      </c>
+      <c r="C2" s="14" t="str">
+        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS: coste del escenario Base")</f>
+        <v>HIPÓTESIS: coste del escenario Base</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="13" t="n">
+        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G15,Escenarios!C15)</f>
+        <v>2.5</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <f aca="false">A6/(1+Supuestos!$B$4)</f>
+        <v>20.5785123966942</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <f aca="false">A6*Supuestos!$B$5+Supuestos!$B$6</f>
+        <v>1.0221</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <f aca="false">B6-$B$2-$B$3-C6</f>
+        <v>3.05641239669422</v>
+      </c>
+      <c r="E6" s="3" t="str">
+        <f aca="false">IF(D6&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
+        <v>No supera (hipótesis)</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <f aca="false">D6-Supuestos!$B$9</f>
+        <v>-6.94358760330579</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <f aca="false">A7/(1+Supuestos!$B$4)</f>
+        <v>24.7107438016529</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <f aca="false">A7*Supuestos!$B$5+Supuestos!$B$6</f>
+        <v>1.1671</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <f aca="false">B7-$B$2-$B$3-C7</f>
+        <v>7.04364380165289</v>
+      </c>
+      <c r="E7" s="3" t="str">
+        <f aca="false">IF(D7&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <f aca="false">D7-Supuestos!$B$9</f>
+        <v>-2.95635619834711</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <f aca="false">A8/(1+Supuestos!$B$4)</f>
+        <v>28.8429752066116</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <f aca="false">A8*Supuestos!$B$5+Supuestos!$B$6</f>
+        <v>1.3121</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <f aca="false">B8-$B$2-$B$3-C8</f>
+        <v>11.0308752066116</v>
+      </c>
+      <c r="E8" s="3" t="str">
+        <f aca="false">IF(D8&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
+        <v>Supera umbral (hipótesis)</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <f aca="false">D8-Supuestos!$B$9</f>
+        <v>1.03087520661157</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <f aca="false">Supuestos!B10</f>
+        <v>5</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G14,Escenarios!C14)</f>
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="str">
+        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS (Base)")</f>
+        <v>HIPÓTESIS (Base)</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <f aca="false">B4*B5*B6+B7*B6</f>
+        <v>98</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <f aca="false">Supuestos!B8</f>
+        <v>50</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <f aca="false">IF(B9&gt;=B8,"Sí","INSUFICIENTE")</f>
+        <v>INSUFICIENTE</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <f aca="false">IF(B5*B6=0,"—",MAX(0,(B9-B7*B6)/(B5*B6)))</f>
+        <v>0.314285714285714</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="2" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20" t="str">
+        <f aca="false">IF(OR(B4="",B4=0,F4=""),"",F4/B4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="20" t="str">
+        <f aca="false">IF(OR(C4="",C4=0,D4=""),"",D4/C4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="str">
+        <f aca="false">IF(OR(D4="",D4=0,E4=""),"",E4/D4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="11" t="str">
+        <f aca="false">IF(OR(F4="",F4=0,G4=""),"",G4/F4)</f>
+        <v/>
+      </c>
+      <c r="O4" s="11" t="str">
+        <f aca="false">IF(OR(F4="",F4=0,H4=""),"",(H4+IF(I4="",0,I4))/F4)</f>
+        <v/>
+      </c>
+      <c r="P4" s="11" t="str">
+        <f aca="false">IF(F4="","",IF(Escenarios!$G$13="COMPLETO",F4*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="20" t="str">
+        <f aca="false">IF(OR(F4="",F4=0,J4=""),"",J4/F4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="20" t="str">
+        <f aca="false">IF(OR(B5="",B5=0,F5=""),"",F5/B5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="20" t="str">
+        <f aca="false">IF(OR(C5="",C5=0,D5=""),"",D5/C5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="20" t="str">
+        <f aca="false">IF(OR(D5="",D5=0,E5=""),"",E5/D5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="11" t="str">
+        <f aca="false">IF(OR(F5="",F5=0,G5=""),"",G5/F5)</f>
+        <v/>
+      </c>
+      <c r="O5" s="11" t="str">
+        <f aca="false">IF(OR(F5="",F5=0,H5=""),"",(H5+IF(I5="",0,I5))/F5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="11" t="str">
+        <f aca="false">IF(F5="","",IF(Escenarios!$G$13="COMPLETO",F5*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="20" t="str">
+        <f aca="false">IF(OR(F5="",F5=0,J5=""),"",J5/F5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20" t="str">
+        <f aca="false">IF(OR(B6="",B6=0,F6=""),"",F6/B6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="20" t="str">
+        <f aca="false">IF(OR(C6="",C6=0,D6=""),"",D6/C6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="20" t="str">
+        <f aca="false">IF(OR(D6="",D6=0,E6=""),"",E6/D6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="11" t="str">
+        <f aca="false">IF(OR(F6="",F6=0,G6=""),"",G6/F6)</f>
+        <v/>
+      </c>
+      <c r="O6" s="11" t="str">
+        <f aca="false">IF(OR(F6="",F6=0,H6=""),"",(H6+IF(I6="",0,I6))/F6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="11" t="str">
+        <f aca="false">IF(F6="","",IF(Escenarios!$G$13="COMPLETO",F6*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="20" t="str">
+        <f aca="false">IF(OR(F6="",F6=0,J6=""),"",J6/F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="20" t="str">
+        <f aca="false">IF(OR(B7="",B7=0,F7=""),"",F7/B7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="20" t="str">
+        <f aca="false">IF(OR(C7="",C7=0,D7=""),"",D7/C7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="20" t="str">
+        <f aca="false">IF(OR(D7="",D7=0,E7=""),"",E7/D7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="11" t="str">
+        <f aca="false">IF(OR(F7="",F7=0,G7=""),"",G7/F7)</f>
+        <v/>
+      </c>
+      <c r="O7" s="11" t="str">
+        <f aca="false">IF(OR(F7="",F7=0,H7=""),"",(H7+IF(I7="",0,I7))/F7)</f>
+        <v/>
+      </c>
+      <c r="P7" s="11" t="str">
+        <f aca="false">IF(F7="","",IF(Escenarios!$G$13="COMPLETO",F7*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="20" t="str">
+        <f aca="false">IF(OR(F7="",F7=0,J7=""),"",J7/F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="20" t="str">
+        <f aca="false">IF(OR(B8="",B8=0,F8=""),"",F8/B8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="20" t="str">
+        <f aca="false">IF(OR(C8="",C8=0,D8=""),"",D8/C8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="20" t="str">
+        <f aca="false">IF(OR(D8="",D8=0,E8=""),"",E8/D8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="11" t="str">
+        <f aca="false">IF(OR(F8="",F8=0,G8=""),"",G8/F8)</f>
+        <v/>
+      </c>
+      <c r="O8" s="11" t="str">
+        <f aca="false">IF(OR(F8="",F8=0,H8=""),"",(H8+IF(I8="",0,I8))/F8)</f>
+        <v/>
+      </c>
+      <c r="P8" s="11" t="str">
+        <f aca="false">IF(F8="","",IF(Escenarios!$G$13="COMPLETO",F8*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="20" t="str">
+        <f aca="false">IF(OR(F8="",F8=0,J8=""),"",J8/F8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="20" t="str">
+        <f aca="false">IF(OR(B9="",B9=0,F9=""),"",F9/B9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="20" t="str">
+        <f aca="false">IF(OR(C9="",C9=0,D9=""),"",D9/C9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="20" t="str">
+        <f aca="false">IF(OR(D9="",D9=0,E9=""),"",E9/D9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="11" t="str">
+        <f aca="false">IF(OR(F9="",F9=0,G9=""),"",G9/F9)</f>
+        <v/>
+      </c>
+      <c r="O9" s="11" t="str">
+        <f aca="false">IF(OR(F9="",F9=0,H9=""),"",(H9+IF(I9="",0,I9))/F9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="11" t="str">
+        <f aca="false">IF(F9="","",IF(Escenarios!$G$13="COMPLETO",F9*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="20" t="str">
+        <f aca="false">IF(OR(F9="",F9=0,J9=""),"",J9/F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="20" t="str">
+        <f aca="false">IF(OR(B10="",B10=0,F10=""),"",F10/B10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="20" t="str">
+        <f aca="false">IF(OR(C10="",C10=0,D10=""),"",D10/C10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="20" t="str">
+        <f aca="false">IF(OR(D10="",D10=0,E10=""),"",E10/D10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="11" t="str">
+        <f aca="false">IF(OR(F10="",F10=0,G10=""),"",G10/F10)</f>
+        <v/>
+      </c>
+      <c r="O10" s="11" t="str">
+        <f aca="false">IF(OR(F10="",F10=0,H10=""),"",(H10+IF(I10="",0,I10))/F10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="11" t="str">
+        <f aca="false">IF(F10="","",IF(Escenarios!$G$13="COMPLETO",F10*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="20" t="str">
+        <f aca="false">IF(OR(F10="",F10=0,J10=""),"",J10/F10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="20" t="str">
+        <f aca="false">IF(OR(B11="",B11=0,F11=""),"",F11/B11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="20" t="str">
+        <f aca="false">IF(OR(C11="",C11=0,D11=""),"",D11/C11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="20" t="str">
+        <f aca="false">IF(OR(D11="",D11=0,E11=""),"",E11/D11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="11" t="str">
+        <f aca="false">IF(OR(F11="",F11=0,G11=""),"",G11/F11)</f>
+        <v/>
+      </c>
+      <c r="O11" s="11" t="str">
+        <f aca="false">IF(OR(F11="",F11=0,H11=""),"",(H11+IF(I11="",0,I11))/F11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="11" t="str">
+        <f aca="false">IF(F11="","",IF(Escenarios!$G$13="COMPLETO",F11*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="20" t="str">
+        <f aca="false">IF(OR(F11="",F11=0,J11=""),"",J11/F11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="20" t="str">
+        <f aca="false">IF(OR(B12="",B12=0,F12=""),"",F12/B12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="20" t="str">
+        <f aca="false">IF(OR(C12="",C12=0,D12=""),"",D12/C12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="20" t="str">
+        <f aca="false">IF(OR(D12="",D12=0,E12=""),"",E12/D12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="11" t="str">
+        <f aca="false">IF(OR(F12="",F12=0,G12=""),"",G12/F12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="11" t="str">
+        <f aca="false">IF(OR(F12="",F12=0,H12=""),"",(H12+IF(I12="",0,I12))/F12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="11" t="str">
+        <f aca="false">IF(F12="","",IF(Escenarios!$G$13="COMPLETO",F12*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="20" t="str">
+        <f aca="false">IF(OR(F12="",F12=0,J12=""),"",J12/F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="20" t="str">
+        <f aca="false">IF(OR(B13="",B13=0,F13=""),"",F13/B13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="20" t="str">
+        <f aca="false">IF(OR(C13="",C13=0,D13=""),"",D13/C13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="20" t="str">
+        <f aca="false">IF(OR(D13="",D13=0,E13=""),"",E13/D13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="11" t="str">
+        <f aca="false">IF(OR(F13="",F13=0,G13=""),"",G13/F13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="11" t="str">
+        <f aca="false">IF(OR(F13="",F13=0,H13=""),"",(H13+IF(I13="",0,I13))/F13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="11" t="str">
+        <f aca="false">IF(F13="","",IF(Escenarios!$G$13="COMPLETO",F13*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="20" t="str">
+        <f aca="false">IF(OR(F13="",F13=0,J13=""),"",J13/F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="20" t="str">
+        <f aca="false">IF(OR(B14="",B14=0,F14=""),"",F14/B14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="20" t="str">
+        <f aca="false">IF(OR(C14="",C14=0,D14=""),"",D14/C14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="20" t="str">
+        <f aca="false">IF(OR(D14="",D14=0,E14=""),"",E14/D14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="11" t="str">
+        <f aca="false">IF(OR(F14="",F14=0,G14=""),"",G14/F14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="11" t="str">
+        <f aca="false">IF(OR(F14="",F14=0,H14=""),"",(H14+IF(I14="",0,I14))/F14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="11" t="str">
+        <f aca="false">IF(F14="","",IF(Escenarios!$G$13="COMPLETO",F14*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="20" t="str">
+        <f aca="false">IF(OR(F14="",F14=0,J14=""),"",J14/F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="20" t="str">
+        <f aca="false">IF(OR(B15="",B15=0,F15=""),"",F15/B15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="20" t="str">
+        <f aca="false">IF(OR(C15="",C15=0,D15=""),"",D15/C15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="20" t="str">
+        <f aca="false">IF(OR(D15="",D15=0,E15=""),"",E15/D15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="11" t="str">
+        <f aca="false">IF(OR(F15="",F15=0,G15=""),"",G15/F15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="11" t="str">
+        <f aca="false">IF(OR(F15="",F15=0,H15=""),"",(H15+IF(I15="",0,I15))/F15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="11" t="str">
+        <f aca="false">IF(F15="","",IF(Escenarios!$G$13="COMPLETO",F15*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="20" t="str">
+        <f aca="false">IF(OR(F15="",F15=0,J15=""),"",J15/F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1343,14 +2628,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="12" t="n">
-        <f aca="false">Escenarios!C15</f>
+      <c r="C2" s="13" t="n">
+        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G21,Escenarios!C21)</f>
         <v>7.04364380165289</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="str">
+        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS (Base)")</f>
+        <v>HIPÓTESIS (Base)</v>
+      </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1360,118 +2648,102 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>62</v>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="19" t="n">
         <v>300</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="17" t="n">
         <f aca="false">A5*B5</f>
         <v>1.5</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="11" t="n">
         <f aca="false">C5*$C$2</f>
         <v>10.5654657024793</v>
       </c>
-      <c r="E5" s="16" t="n">
-        <f aca="false">C5*Escenarios!$C$11</f>
+      <c r="E5" s="11" t="n">
+        <f aca="false">C5*'Capital circulante'!$B$6</f>
         <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="19" t="n">
         <v>1000</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="17" t="n">
         <f aca="false">A6*B6</f>
         <v>10</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">C6*$C$2</f>
         <v>70.4364380165289</v>
       </c>
-      <c r="E6" s="16" t="n">
-        <f aca="false">C6*Escenarios!$C$11</f>
+      <c r="E6" s="11" t="n">
+        <f aca="false">C6*'Capital circulante'!$B$6</f>
         <v>140</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="19" t="n">
         <v>3000</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="17" t="n">
         <f aca="false">A7*B7</f>
         <v>30</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="11" t="n">
         <f aca="false">C7*$C$2</f>
         <v>211.309314049587</v>
       </c>
-      <c r="E7" s="16" t="n">
-        <f aca="false">C7*Escenarios!$C$11</f>
+      <c r="E7" s="11" t="n">
+        <f aca="false">C7*'Capital circulante'!$B$6</f>
         <v>420</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="19" t="n">
         <v>10000</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0.015</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="17" t="n">
         <f aca="false">A8*B8</f>
         <v>150</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="11" t="n">
         <f aca="false">C8*$C$2</f>
         <v>1056.54657024793</v>
       </c>
-      <c r="E8" s="16" t="n">
-        <f aca="false">C8*Escenarios!$C$11</f>
+      <c r="E8" s="11" t="n">
+        <f aca="false">C8*'Capital circulante'!$B$6</f>
         <v>2100</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/05_ECONOMIA_UNITARIA.xlsx
+++ b/docs/05_ECONOMIA_UNITARIA.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="Leyenda" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Supuestos" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Escenarios" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Costes variables" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Test de precio" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Capital circulante" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Panel semanal" sheetId="6" state="visible" r:id="rId8"/>
@@ -26,51 +26,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
-  <si>
-    <t xml:space="preserve">Economía unitaria · Descanso Compartido · V2 (13/10/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninguna cifra de este libro es un coste o precio real confirmado salvo lo que el titular escriba en la columna REAL con facturas o cotizaciones firmadas.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="124">
+  <si>
+    <t xml:space="preserve">Economía unitaria · VINCIRENA (marca provisional) · Mercado EE. UU. · USD · V2.1 (13/10/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninguna celda contiene costes, precios ni umbrales reales: se rellenan con cotizaciones, facturas y decisiones del titular. Mientras falte un dato obligatorio, la hoja muestra «DATOS INCOMPLETOS».</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo usarlo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Celdas AMARILLAS con texto AZUL = datos editables. Texto NEGRO = fórmulas (no sobrescribir). VERDE = enlace a otra hoja.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Columna REAL (hoja Escenarios): rellenar las 5 partidas del coste (filas 7–11). Si falta UNA, la columna muestra «DATOS INCOMPLETOS» y no calcula margen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Una partida que realmente vale 0 se escribe 0; una celda VACÍA significa «no lo sé» y bloquea el cálculo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Escenarios 1–5 = hipótesis de los informes (coste agregado). Reproducen 0,56 / 7,04 / 11,54 / 11,03 / 7,14 €.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Veredictos posibles: «Supera umbral (hipótesis)», «No supera (hipótesis)», «Supera umbral», «No supera», «DATOS INCOMPLETOS». Nunca «rentable».</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formato esperado de una fila del panel semanal (ejemplo de FORMATO, no son datos): semana 2026-W43 · sesiones 1.000 · sesiones con vista de producto 400 · con ATC 40 · con checkout 20 · pedidos 10 · ventas brutas 299,00 € …</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuentes de los supuestos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVA 21 %: tipo general (AEAT, S25); tipo del SKU pendiente de confirmar por asesoría.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión 2,9 % + 0,30 €: supuesto prudencial de los informes; sustituir por la tarifa real del plan (fila «Comisión real»).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liquidación Shopify Payments ≥ 3 días hábiles (S27). Capital 50 €: presupuesto declarado por el titular. CAC 10 €: ejemplo del Estudio §9.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No incluido: cuota Shopify, apps, gestoría, IRPF y publicidad salvo CAC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuestos globales</t>
+    <t xml:space="preserve">1. Celdas AMARILLAS con texto AZUL = datos editables. NEGRO = fórmulas. VERDE = enlaces entre hojas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Rellena «Costes variables» (columna B) con datos reales por unidad/pedido en USD. Una celda VACÍA = «no lo sé» y bloquea el cálculo; un 0 escrito es un dato válido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. «Test de precio»: los precios son PUNTOS DE PRUEBA editables (no precios decididos). Cada fila descuenta TODAS las partidas variables y la comisión real si existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Impuestos: en EE. UU. el precio se muestra sin sales tax; el impuesto se calcula en el checkout y se ingresa al estado. No se resta del precio (a diferencia del IVA español de la V2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. No se modela LTV ni suscripción: el producto es reutilizable. La decisión se basa en el margen del primer pedido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuestos que hay que verificar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de pago: 2,9 % + 0,30 $ es un supuesto de partida (tarifa online publicada para planes básicos de Shopify Payments en EE. UU.); confirmar con el plan contratado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aranceles: el tratamiento de los envíos de bajo valor importados en EE. UU. (de minimis) ha cambiado recientemente; confirmar con el transitario o agente de aduanas antes de rellenar la partida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital: el titular declaró 1–50 € para España; introducir el importe disponible en USD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versión anterior (España, EUR, con IVA): docs/archive/05_ECONOMIA_UNITARIA_ES_V2.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supuestos globales (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">Supuesto</t>
@@ -82,202 +79,229 @@
     <t xml:space="preserve">Fuente / nota</t>
   </si>
   <si>
-    <t xml:space="preserve">IVA aplicado al PVP (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S25 tipo general; tipo del SKU pendiente (asesoría).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión de pago variable (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supuesto de los informes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión de pago fija por pedido (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umbral mínimo de contribución antes de marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estudio §9.2 (7–8 €).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital disponible para pedidos y reembolsos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declarado por el titular.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAC de referencia (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estudio §9.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Días naturales hasta cobrar la liquidación (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S27: mínimo 3 días hábiles + banco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución por pedido (antes de costes fijos e impuestos directos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columnas B–F: hipótesis de los informes. Columna G: REAL (solo datos confirmados).</t>
+    <t xml:space="preserve">Comisión de pago variable (supuesto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar con el plan de Shopify Payments contratado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de pago fija por pedido (supuesto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar con el plan contratado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umbral mínimo de contribución por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisión del titular. Vacío = sin veredicto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital disponible para pedidos y reembolsos (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato del titular.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAC de referencia por cliente (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato o hipótesis del titular. Vacío = no se calcula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días naturales hasta cobrar la liquidación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificar con Shopify Payments (calendario de pagos).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costes variables REALES por pedido de 1 unidad (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo datos confirmados (cotizaciones, facturas, tarifas). Vacío = bloquea el cálculo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obligatoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Producto: coste unitario del proveedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cotización firmada del modelo exacto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flete internacional / inbound por unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prorrateado por unidad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aranceles, tasas y agente de aduanas por unidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmar régimen vigente con el agente de aduanas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envío al cliente (última milla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarifa real del transportista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embalaje y preparación (fulfillment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva por incidencias / contracargos por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pérdidas, daños, fraude.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atención al cliente por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo o herramientas imputables.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contenido / colaboradores / afiliados por venta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste de producción o comisiones por venta. 0 si no hay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasa de devolución esperada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dato real o prudente; 0 % solo si se documenta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste por devolución (envío de vuelta + producto no recuperable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por cada devolución.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso por envío cobrado al cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 si el envío es gratuito para el cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descuento medio por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 si no hay descuentos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de pago variable REAL (opcional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacío = usar Supuestos!B4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de pago fija REAL (opcional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacío = usar Supuestos!B5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partidas obligatorias rellenadas (de 12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste de producto puesto en cliente (filas 4–8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste esperado de devoluciones por pedido (fila 12 × fila 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otros costes variables por pedido (filas 9–11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste variable total por pedido (antes de comisión)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión variable usada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión fija usada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desembolso antes de cobrar (filas 4–8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test de precio · puntos de prueba en USD (no son precios decididos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada fila descuenta TODAS las partidas de «Costes variables» y la comisión real si existe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio de prueba (sin sales tax)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso del pedido (precio − descuento + envío cobrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comisión de pago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste producto puesto en cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devoluciones esperadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incidencias + atención + contenido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución por pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veredicto frente al umbral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución tras CAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comprobación: contribución = ingreso − comisión − coste producto − devoluciones − (incidencias + atención + contenido). Ninguna partida se omite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital necesario antes de cobrar las liquidaciones (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">Concepto</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Desfavorable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Mejor logística</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. PVP superior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Ejemplo Maestro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REAL (confirmado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PVP con IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de columna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIPÓTESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste agregado (solo hipótesis; no se admite en REAL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Envío a domicilio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Aranceles / derecho 3 € / importación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Preparación y embalaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · Otros costes variables no recuperables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partidas del desglose rellenadas (de 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado del coste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste completo usado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva incidencias y soporte por pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste esperado de devoluciones por pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste de contenido / colaboradores por venta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión real % (vacío = usar supuesto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PVP sin IVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión de pago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución por pedido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veredicto frente al umbral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución tras CAC de referencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedidos financiables con el capital (coste completo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fila 13: el fallo de la V1 era IF(SUM(G6:G10)&gt;0,SUM,agregado): con 1 de 5 partidas tomaba ese importe como coste total e inflaba el margen. Ahora 1–4 partidas = DATOS INCOMPLETOS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filas 16–17 de las hipótesis valen 0 para reproducir los informes. En REAL deben rellenarse (0 solo si es real).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ningún veredicto dice «rentable»: superar el umbral antes de marketing no implica beneficio (ver fila 23).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test de precio con el mismo coste (hipótesis — no son precios decididos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste usado:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva incidencias:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PVP con IVA (a probar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comisión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veredicto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tras CAC ref.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital necesario antes de cobrar las liquidaciones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nota</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedidos por día (hipótesis)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Editar: escenario de ventas a cubrir</t>
+    <t xml:space="preserve">Pedidos por día a cubrir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escenario de ventas del titular</t>
   </si>
   <si>
     <t xml:space="preserve">Días hasta cobrar</t>
   </si>
   <si>
-    <t xml:space="preserve">Coste por pedido pagado al proveedor</t>
+    <t xml:space="preserve">Desembolso por pedido antes de cobrar</t>
   </si>
   <si>
     <t xml:space="preserve">Colchón para reembolsos (pedidos equivalentes)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hipótesis</t>
+    <t xml:space="preserve">Decisión del titular</t>
   </si>
   <si>
     <t xml:space="preserve">Capital necesario</t>
@@ -289,10 +313,10 @@
     <t xml:space="preserve">¿Suficiente?</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedidos/día sostenibles sin capital extra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panel semanal (rellenar con datos de Shopify Analytics; sin datos = vacío)</t>
+    <t xml:space="preserve">Panel semanal (datos de Shopify Analytics, en USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio de venta actual (USD, sin sales tax):</t>
   </si>
   <si>
     <t xml:space="preserve">Semana</t>
@@ -313,13 +337,13 @@
     <t xml:space="preserve">Pedidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Ventas brutas (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasto de captación (€)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coste de contenido (€)</t>
+    <t xml:space="preserve">Ventas brutas (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasto de captación (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coste de contenido (USD)</t>
   </si>
   <si>
     <t xml:space="preserve">Devoluciones (nº)</t>
@@ -346,13 +370,19 @@
     <t xml:space="preserve">Tasa devolución</t>
   </si>
   <si>
-    <t xml:space="preserve">Definiciones: conversión = pedidos/sesiones · ATC = sesiones con añadir al carrito / sesiones con vista de producto · Checkout = sesiones con checkout / sesiones con ATC · AOV = ventas brutas / pedidos · CAC = (captación + contenido) / pedidos. Las visualizaciones en redes NO son sesiones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensibilidad de adquisición (hipótesis de planificación)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contribución usada:</t>
+    <t xml:space="preserve">Definiciones: conversión = pedidos/sesiones · ATC = sesiones con añadir al carrito / sesiones con vista de producto · checkout = sesiones con checkout / sesiones con ATC · AOV = ventas brutas / pedidos · CAC = (captación + contenido) / pedidos. Las visualizaciones en redes no son sesiones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensibilidad de adquisición (planificación, no previsión)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución usada (Test de precio, fila elegida):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← 1, 2 o 3 = fila 5, 6 o 7 de «Test de precio»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribución por pedido:</t>
   </si>
   <si>
     <t xml:space="preserve">Sesiones cualificadas/mes</t>
@@ -377,7 +407,7 @@
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot; €&quot;;\(#,##0.00&quot; €)&quot;;\-"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="@"/>
@@ -456,7 +486,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -473,12 +503,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -516,7 +540,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -553,14 +577,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -569,11 +585,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -585,10 +601,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -597,7 +609,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -644,7 +656,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -862,10 +874,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="140"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="150"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -915,36 +927,28 @@
       <c r="A10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
+      <c r="A12" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
+      <c r="A13" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -963,17 +967,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -985,55 +989,51 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>7</v>
-      </c>
+      <c r="B7" s="7"/>
       <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
@@ -1042,9 +1042,7 @@
       <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>50</v>
-      </c>
+      <c r="B8" s="7"/>
       <c r="C8" s="4" t="s">
         <v>26</v>
       </c>
@@ -1053,22 +1051,9 @@
       <c r="A9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="7" t="n">
-        <v>10</v>
-      </c>
+      <c r="B9" s="8"/>
       <c r="C9" s="4" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1087,572 +1072,320 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="G4" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>42</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B5" s="7"/>
       <c r="C5" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>45</v>
+        <v>38</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="C8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="C9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="C11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="10" t="n">
-        <f aca="false">COUNT(B7:B11)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <f aca="false">COUNT(C7:C11)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <f aca="false">COUNT(D7:D11)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <f aca="false">COUNT(E7:E11)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <f aca="false">COUNT(F7:F11)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <f aca="false">COUNT(G7:G11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="3" t="str">
-        <f aca="false">IF(B12=5,"DESGLOSE COMPLETO",IF(AND(B12=0,B6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
-        <v>HIPÓTESIS (agregado)</v>
-      </c>
-      <c r="C13" s="3" t="str">
-        <f aca="false">IF(C12=5,"DESGLOSE COMPLETO",IF(AND(C12=0,C6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
-        <v>HIPÓTESIS (agregado)</v>
-      </c>
-      <c r="D13" s="3" t="str">
-        <f aca="false">IF(D12=5,"DESGLOSE COMPLETO",IF(AND(D12=0,D6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
-        <v>HIPÓTESIS (agregado)</v>
-      </c>
-      <c r="E13" s="3" t="str">
-        <f aca="false">IF(E12=5,"DESGLOSE COMPLETO",IF(AND(E12=0,E6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
-        <v>HIPÓTESIS (agregado)</v>
-      </c>
-      <c r="F13" s="3" t="str">
-        <f aca="false">IF(F12=5,"DESGLOSE COMPLETO",IF(AND(F12=0,F6&lt;&gt;""),"HIPÓTESIS (agregado)","DATOS INCOMPLETOS"))</f>
-        <v>HIPÓTESIS (agregado)</v>
-      </c>
-      <c r="G13" s="3" t="str">
-        <f aca="false">IF(OR(G4="",G12&lt;5,G15="",G16="",G17=""),"DATOS INCOMPLETOS","COMPLETO")</f>
-        <v>DATOS INCOMPLETOS</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="11" t="n">
-        <f aca="false">IF(B13="DATOS INCOMPLETOS","—",IF(B12=5,SUM(B7:B11),B6))</f>
-        <v>16</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <f aca="false">IF(C13="DATOS INCOMPLETOS","—",IF(C12=5,SUM(C7:C11),C6))</f>
-        <v>14</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <f aca="false">IF(D13="DATOS INCOMPLETOS","—",IF(D12=5,SUM(D7:D11),D6))</f>
-        <v>10</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <f aca="false">IF(E13="DATOS INCOMPLETOS","—",IF(E12=5,SUM(E7:E11),E6))</f>
-        <v>14</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <f aca="false">IF(F13="DATOS INCOMPLETOS","—",IF(F12=5,SUM(F7:F11),F6))</f>
-        <v>14.4</v>
-      </c>
-      <c r="G14" s="11" t="str">
-        <f aca="false">IF(G13="DATOS INCOMPLETOS","—",IF(G12=5,SUM(G7:G11),G6))</f>
-        <v>—</v>
+      <c r="B14" s="7"/>
+      <c r="C14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <f aca="false">COUNT(B4:B15)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <f aca="false">IF(B4="","—",B4/(1+Supuestos!$B$4))</f>
-        <v>20.5785123966942</v>
-      </c>
-      <c r="C19" s="11" t="n">
-        <f aca="false">IF(C4="","—",C4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <f aca="false">IF(D4="","—",D4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <f aca="false">IF(E4="","—",E4/(1+Supuestos!$B$4))</f>
-        <v>28.8429752066116</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <f aca="false">IF(F4="","—",F4/(1+Supuestos!$B$4))</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(G4="","—",G4/(1+Supuestos!$B$4))</f>
-        <v>—</v>
-      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="11" t="n">
-        <f aca="false">IF(B4="","—",B4*IF(B18="",Supuestos!$B$5,B18)+Supuestos!$B$6)</f>
-        <v>1.0221</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <f aca="false">IF(C4="","—",C4*IF(C18="",Supuestos!$B$5,C18)+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="D20" s="11" t="n">
-        <f aca="false">IF(D4="","—",D4*IF(D18="",Supuestos!$B$5,D18)+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <f aca="false">IF(E4="","—",E4*IF(E18="",Supuestos!$B$5,E18)+Supuestos!$B$6)</f>
-        <v>1.3121</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <f aca="false">IF(F4="","—",F4*IF(F18="",Supuestos!$B$5,F18)+Supuestos!$B$6)</f>
-        <v>1.1671</v>
-      </c>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(G4="","—",G4*IF(G18="",Supuestos!$B$5,G18)+Supuestos!$B$6)</f>
-        <v>—</v>
-      </c>
+      <c r="A20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="2" t="str">
+        <f aca="false">IF(B19=12,"COMPLETO","DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",B19-B14-B15-B16-B17-B20,"DATOS INCOMPLETOS")</f>
-        <v>0.556412396694215</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",C19-C14-C15-C16-C17-C20,"DATOS INCOMPLETOS")</f>
-        <v>7.04364380165289</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",D19-D14-D15-D16-D17-D20,"DATOS INCOMPLETOS")</f>
-        <v>11.5436438016529</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",E19-E14-E15-E16-E17-E20,"DATOS INCOMPLETOS")</f>
-        <v>11.0308752066116</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",F19-F14-F15-F16-F17-F20,"DATOS INCOMPLETOS")</f>
-        <v>7.14364380165289</v>
-      </c>
-      <c r="G21" s="12" t="str">
-        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",G19-G14-G15-G16-G17-G20,"DATOS INCOMPLETOS")</f>
-        <v>DATOS INCOMPLETOS</v>
-      </c>
+      <c r="A21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="9" t="str">
+        <f aca="false">IF($B$20="COMPLETO",SUM(B4:B8),"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="2" t="str">
-        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",IF(B21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
-        <v>No supera (hipótesis)</v>
-      </c>
-      <c r="C22" s="2" t="str">
-        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",IF(C21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="D22" s="2" t="str">
-        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",IF(D21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",IF(E21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="F22" s="2" t="str">
-        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",IF(F21&gt;=Supuestos!$B$7,"Supera umbral (hipótesis)","No supera (hipótesis)"),"DATOS INCOMPLETOS")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="G22" s="2" t="str">
-        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",IF(G21&gt;=Supuestos!$B$7,"Supera umbral","No supera"),"DATOS INCOMPLETOS")</f>
-        <v>DATOS INCOMPLETOS</v>
-      </c>
+      <c r="A22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="9" t="str">
+        <f aca="false">IF($B$20="COMPLETO",B12*B13,"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="11" t="n">
-        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",B21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>-9.44358760330579</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",C21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>-2.95635619834711</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",D21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>1.54364380165289</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",E21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>1.03087520661157</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",F21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>-2.85635619834711</v>
-      </c>
-      <c r="G23" s="11" t="str">
-        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",G21-Supuestos!$B$9,"DATOS INCOMPLETOS")</f>
-        <v>DATOS INCOMPLETOS</v>
-      </c>
+      <c r="A23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="9" t="str">
+        <f aca="false">IF($B$20="COMPLETO",SUM(B9:B11),"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="10" t="n">
-        <f aca="false">IF(B13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/B14),"DATOS INCOMPLETOS")</f>
-        <v>3</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <f aca="false">IF(C13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/C14),"DATOS INCOMPLETOS")</f>
-        <v>3</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <f aca="false">IF(D13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/D14),"DATOS INCOMPLETOS")</f>
-        <v>5</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <f aca="false">IF(E13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/E14),"DATOS INCOMPLETOS")</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <f aca="false">IF(F13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/F14),"DATOS INCOMPLETOS")</f>
-        <v>3</v>
-      </c>
-      <c r="G24" s="10" t="str">
-        <f aca="false">IF(G13&lt;&gt;"DATOS INCOMPLETOS",INT(Supuestos!$B$8/G14),"DATOS INCOMPLETOS")</f>
-        <v>DATOS INCOMPLETOS</v>
-      </c>
+      <c r="A24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="10" t="str">
+        <f aca="false">IF($B$20="COMPLETO",B21+B22+B23,"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="11" t="n">
+        <f aca="false">IF(B16="",Supuestos!B4,B16)</f>
+        <v>0.029</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="9" t="n">
+        <f aca="false">IF(B17="",Supuestos!B5,B17)</f>
+        <v>0.3</v>
+      </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="9" t="str">
+        <f aca="false">IF($B$20="COMPLETO",SUM(B4:B8),"DATOS INCOMPLETOS")</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B13:G24">
+  <conditionalFormatting sqref="B20:B27">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>B13="DATOS INCOMPLETOS"</formula>
+      <formula>B20="DATOS INCOMPLETOS"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1670,160 +1403,227 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="13" t="n">
-        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G14,Escenarios!C14)</f>
-        <v>14</v>
-      </c>
-      <c r="C2" s="14" t="str">
-        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS: coste del escenario Base")</f>
-        <v>HIPÓTESIS: coste del escenario Base</v>
-      </c>
+      <c r="A2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="13" t="n">
-        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G15,Escenarios!C15)</f>
-        <v>2.5</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>75</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="B5" s="9" t="n">
+        <f aca="false">IF(A5="","—",A5-'Costes variables'!$B$15+'Costes variables'!$B$14)</f>
+        <v>24.99</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <f aca="false">IF(A5="","—",B5*'Costes variables'!$B$25+'Costes variables'!$B$26)</f>
+        <v>1.02471</v>
+      </c>
+      <c r="D5" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$21</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="E5" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$22</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="F5" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$23</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="G5" s="10" t="str">
+        <f aca="false">IF(OR(A5="",NOT('Costes variables'!$B$20="COMPLETO")),"DATOS INCOMPLETOS",B5-C5-D5-E5-F5)</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="H5" s="2" t="str">
+        <f aca="false">IF(G5="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$6="","Umbral sin definir",IF(G5&gt;=Supuestos!$B$6,"Supera umbral","No supera")))</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="I5" s="9" t="str">
+        <f aca="false">IF(G5="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$8="","CAC sin definir",G5-Supuestos!$B$8))</f>
+        <v>DATOS INCOMPLETOS</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <f aca="false">A6/(1+Supuestos!$B$4)</f>
-        <v>20.5785123966942</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <f aca="false">A6*Supuestos!$B$5+Supuestos!$B$6</f>
-        <v>1.0221</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <f aca="false">B6-$B$2-$B$3-C6</f>
-        <v>3.05641239669422</v>
-      </c>
-      <c r="E6" s="3" t="str">
-        <f aca="false">IF(D6&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
-        <v>No supera (hipótesis)</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <f aca="false">D6-Supuestos!$B$9</f>
-        <v>-6.94358760330579</v>
+        <v>29.99</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">IF(A6="","—",A6-'Costes variables'!$B$15+'Costes variables'!$B$14)</f>
+        <v>29.99</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">IF(A6="","—",B6*'Costes variables'!$B$25+'Costes variables'!$B$26)</f>
+        <v>1.16971</v>
+      </c>
+      <c r="D6" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$21</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="E6" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$22</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="F6" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$23</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="G6" s="10" t="str">
+        <f aca="false">IF(OR(A6="",NOT('Costes variables'!$B$20="COMPLETO")),"DATOS INCOMPLETOS",B6-C6-D6-E6-F6)</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="H6" s="2" t="str">
+        <f aca="false">IF(G6="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$6="","Umbral sin definir",IF(G6&gt;=Supuestos!$B$6,"Supera umbral","No supera")))</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="I6" s="9" t="str">
+        <f aca="false">IF(G6="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$8="","CAC sin definir",G6-Supuestos!$B$8))</f>
+        <v>DATOS INCOMPLETOS</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <f aca="false">A7/(1+Supuestos!$B$4)</f>
-        <v>24.7107438016529</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <f aca="false">A7*Supuestos!$B$5+Supuestos!$B$6</f>
-        <v>1.1671</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <f aca="false">B7-$B$2-$B$3-C7</f>
-        <v>7.04364380165289</v>
-      </c>
-      <c r="E7" s="3" t="str">
-        <f aca="false">IF(D7&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <f aca="false">D7-Supuestos!$B$9</f>
-        <v>-2.95635619834711</v>
+        <v>34.99</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <f aca="false">IF(A7="","—",A7-'Costes variables'!$B$15+'Costes variables'!$B$14)</f>
+        <v>34.99</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">IF(A7="","—",B7*'Costes variables'!$B$25+'Costes variables'!$B$26)</f>
+        <v>1.31471</v>
+      </c>
+      <c r="D7" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$21</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="E7" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$22</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="F7" s="12" t="str">
+        <f aca="false">'Costes variables'!$B$23</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="G7" s="10" t="str">
+        <f aca="false">IF(OR(A7="",NOT('Costes variables'!$B$20="COMPLETO")),"DATOS INCOMPLETOS",B7-C7-D7-E7-F7)</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="H7" s="2" t="str">
+        <f aca="false">IF(G7="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$6="","Umbral sin definir",IF(G7&gt;=Supuestos!$B$6,"Supera umbral","No supera")))</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="I7" s="9" t="str">
+        <f aca="false">IF(G7="DATOS INCOMPLETOS","DATOS INCOMPLETOS",IF(Supuestos!$B$8="","CAC sin definir",G7-Supuestos!$B$8))</f>
+        <v>DATOS INCOMPLETOS</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <f aca="false">A8/(1+Supuestos!$B$4)</f>
-        <v>28.8429752066116</v>
-      </c>
-      <c r="C8" s="11" t="n">
-        <f aca="false">A8*Supuestos!$B$5+Supuestos!$B$6</f>
-        <v>1.3121</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <f aca="false">B8-$B$2-$B$3-C8</f>
-        <v>11.0308752066116</v>
-      </c>
-      <c r="E8" s="3" t="str">
-        <f aca="false">IF(D8&gt;=Supuestos!$B$7,"Supera umbral","No supera")&amp;IF($C$2="REAL",""," (hipótesis)")</f>
-        <v>Supera umbral (hipótesis)</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <f aca="false">D8-Supuestos!$B$9</f>
-        <v>1.03087520661157</v>
-      </c>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G5:I7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>G5="DATOS INCOMPLETOS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1839,7 +1639,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -1849,7 +1649,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1861,99 +1661,82 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="15" t="n">
-        <v>1</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="B4" s="13"/>
       <c r="C4" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" s="16" t="n">
-        <f aca="false">Supuestos!B10</f>
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <f aca="false">Supuestos!B9</f>
+        <v>0</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="13" t="n">
-        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G14,Escenarios!C14)</f>
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="str">
-        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS (Base)")</f>
-        <v>HIPÓTESIS (Base)</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="B6" s="12" t="str">
+        <f aca="false">'Costes variables'!B27</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>2</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="B7" s="8"/>
       <c r="C7" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <f aca="false">B4*B5*B6+B7*B6</f>
-        <v>98</v>
+        <v>92</v>
+      </c>
+      <c r="B8" s="10" t="str">
+        <f aca="false">IF(OR(B4="",B5="",B7="",B6="DATOS INCOMPLETOS"),"DATOS INCOMPLETOS",B4*B5*B6+B7*B6)</f>
+        <v>DATOS INCOMPLETOS</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <f aca="false">Supuestos!B8</f>
-        <v>50</v>
+        <v>93</v>
+      </c>
+      <c r="B9" s="12" t="str">
+        <f aca="false">IF(Supuestos!B7="","—",Supuestos!B7)</f>
+        <v>—</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B10" s="2" t="str">
-        <f aca="false">IF(B9&gt;=B8,"Sí","INSUFICIENTE")</f>
-        <v>INSUFICIENTE</v>
+        <f aca="false">IF(OR(B8="DATOS INCOMPLETOS",B9="—"),"DATOS INCOMPLETOS",IF(B9&gt;=B8,"Sí","INSUFICIENTE"))</f>
+        <v>DATOS INCOMPLETOS</v>
       </c>
       <c r="C10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="17" t="n">
-        <f aca="false">IF(B5*B6=0,"—",MAX(0,(B9-B7*B6)/(B5*B6)))</f>
-        <v>0.314285714285714</v>
-      </c>
-      <c r="C11" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1974,13 +1757,12 @@
   <dimension ref="A1:Q17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="1" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2000,10 +1782,12 @@
       <c r="Q1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="D2" s="7"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -2020,533 +1804,533 @@
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="20" t="str">
+      <c r="J4" s="16"/>
+      <c r="K4" s="11" t="str">
         <f aca="false">IF(OR(B4="",B4=0,F4=""),"",F4/B4)</f>
         <v/>
       </c>
-      <c r="L4" s="20" t="str">
+      <c r="L4" s="11" t="str">
         <f aca="false">IF(OR(C4="",C4=0,D4=""),"",D4/C4)</f>
         <v/>
       </c>
-      <c r="M4" s="20" t="str">
+      <c r="M4" s="11" t="str">
         <f aca="false">IF(OR(D4="",D4=0,E4=""),"",E4/D4)</f>
         <v/>
       </c>
-      <c r="N4" s="11" t="str">
+      <c r="N4" s="9" t="str">
         <f aca="false">IF(OR(F4="",F4=0,G4=""),"",G4/F4)</f>
         <v/>
       </c>
-      <c r="O4" s="11" t="str">
+      <c r="O4" s="9" t="str">
         <f aca="false">IF(OR(F4="",F4=0,H4=""),"",(H4+IF(I4="",0,I4))/F4)</f>
         <v/>
       </c>
-      <c r="P4" s="11" t="str">
-        <f aca="false">IF(F4="","",IF(Escenarios!$G$13="COMPLETO",F4*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="20" t="str">
+      <c r="P4" s="9" t="str">
+        <f aca="false">IF(F4="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F4*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q4" s="11" t="str">
         <f aca="false">IF(OR(F4="",F4=0,J4=""),"",J4/F4)</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20" t="str">
+      <c r="J5" s="16"/>
+      <c r="K5" s="11" t="str">
         <f aca="false">IF(OR(B5="",B5=0,F5=""),"",F5/B5)</f>
         <v/>
       </c>
-      <c r="L5" s="20" t="str">
+      <c r="L5" s="11" t="str">
         <f aca="false">IF(OR(C5="",C5=0,D5=""),"",D5/C5)</f>
         <v/>
       </c>
-      <c r="M5" s="20" t="str">
+      <c r="M5" s="11" t="str">
         <f aca="false">IF(OR(D5="",D5=0,E5=""),"",E5/D5)</f>
         <v/>
       </c>
-      <c r="N5" s="11" t="str">
+      <c r="N5" s="9" t="str">
         <f aca="false">IF(OR(F5="",F5=0,G5=""),"",G5/F5)</f>
         <v/>
       </c>
-      <c r="O5" s="11" t="str">
+      <c r="O5" s="9" t="str">
         <f aca="false">IF(OR(F5="",F5=0,H5=""),"",(H5+IF(I5="",0,I5))/F5)</f>
         <v/>
       </c>
-      <c r="P5" s="11" t="str">
-        <f aca="false">IF(F5="","",IF(Escenarios!$G$13="COMPLETO",F5*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="20" t="str">
+      <c r="P5" s="9" t="str">
+        <f aca="false">IF(F5="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F5*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q5" s="11" t="str">
         <f aca="false">IF(OR(F5="",F5=0,J5=""),"",J5/F5)</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="20" t="str">
+      <c r="J6" s="16"/>
+      <c r="K6" s="11" t="str">
         <f aca="false">IF(OR(B6="",B6=0,F6=""),"",F6/B6)</f>
         <v/>
       </c>
-      <c r="L6" s="20" t="str">
+      <c r="L6" s="11" t="str">
         <f aca="false">IF(OR(C6="",C6=0,D6=""),"",D6/C6)</f>
         <v/>
       </c>
-      <c r="M6" s="20" t="str">
+      <c r="M6" s="11" t="str">
         <f aca="false">IF(OR(D6="",D6=0,E6=""),"",E6/D6)</f>
         <v/>
       </c>
-      <c r="N6" s="11" t="str">
+      <c r="N6" s="9" t="str">
         <f aca="false">IF(OR(F6="",F6=0,G6=""),"",G6/F6)</f>
         <v/>
       </c>
-      <c r="O6" s="11" t="str">
+      <c r="O6" s="9" t="str">
         <f aca="false">IF(OR(F6="",F6=0,H6=""),"",(H6+IF(I6="",0,I6))/F6)</f>
         <v/>
       </c>
-      <c r="P6" s="11" t="str">
-        <f aca="false">IF(F6="","",IF(Escenarios!$G$13="COMPLETO",F6*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="20" t="str">
+      <c r="P6" s="9" t="str">
+        <f aca="false">IF(F6="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F6*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="11" t="str">
         <f aca="false">IF(OR(F6="",F6=0,J6=""),"",J6/F6)</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20" t="str">
+      <c r="J7" s="16"/>
+      <c r="K7" s="11" t="str">
         <f aca="false">IF(OR(B7="",B7=0,F7=""),"",F7/B7)</f>
         <v/>
       </c>
-      <c r="L7" s="20" t="str">
+      <c r="L7" s="11" t="str">
         <f aca="false">IF(OR(C7="",C7=0,D7=""),"",D7/C7)</f>
         <v/>
       </c>
-      <c r="M7" s="20" t="str">
+      <c r="M7" s="11" t="str">
         <f aca="false">IF(OR(D7="",D7=0,E7=""),"",E7/D7)</f>
         <v/>
       </c>
-      <c r="N7" s="11" t="str">
+      <c r="N7" s="9" t="str">
         <f aca="false">IF(OR(F7="",F7=0,G7=""),"",G7/F7)</f>
         <v/>
       </c>
-      <c r="O7" s="11" t="str">
+      <c r="O7" s="9" t="str">
         <f aca="false">IF(OR(F7="",F7=0,H7=""),"",(H7+IF(I7="",0,I7))/F7)</f>
         <v/>
       </c>
-      <c r="P7" s="11" t="str">
-        <f aca="false">IF(F7="","",IF(Escenarios!$G$13="COMPLETO",F7*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="20" t="str">
+      <c r="P7" s="9" t="str">
+        <f aca="false">IF(F7="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F7*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="11" t="str">
         <f aca="false">IF(OR(F7="",F7=0,J7=""),"",J7/F7)</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20" t="str">
+      <c r="J8" s="16"/>
+      <c r="K8" s="11" t="str">
         <f aca="false">IF(OR(B8="",B8=0,F8=""),"",F8/B8)</f>
         <v/>
       </c>
-      <c r="L8" s="20" t="str">
+      <c r="L8" s="11" t="str">
         <f aca="false">IF(OR(C8="",C8=0,D8=""),"",D8/C8)</f>
         <v/>
       </c>
-      <c r="M8" s="20" t="str">
+      <c r="M8" s="11" t="str">
         <f aca="false">IF(OR(D8="",D8=0,E8=""),"",E8/D8)</f>
         <v/>
       </c>
-      <c r="N8" s="11" t="str">
+      <c r="N8" s="9" t="str">
         <f aca="false">IF(OR(F8="",F8=0,G8=""),"",G8/F8)</f>
         <v/>
       </c>
-      <c r="O8" s="11" t="str">
+      <c r="O8" s="9" t="str">
         <f aca="false">IF(OR(F8="",F8=0,H8=""),"",(H8+IF(I8="",0,I8))/F8)</f>
         <v/>
       </c>
-      <c r="P8" s="11" t="str">
-        <f aca="false">IF(F8="","",IF(Escenarios!$G$13="COMPLETO",F8*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="20" t="str">
+      <c r="P8" s="9" t="str">
+        <f aca="false">IF(F8="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F8*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="11" t="str">
         <f aca="false">IF(OR(F8="",F8=0,J8=""),"",J8/F8)</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20" t="str">
+      <c r="J9" s="16"/>
+      <c r="K9" s="11" t="str">
         <f aca="false">IF(OR(B9="",B9=0,F9=""),"",F9/B9)</f>
         <v/>
       </c>
-      <c r="L9" s="20" t="str">
+      <c r="L9" s="11" t="str">
         <f aca="false">IF(OR(C9="",C9=0,D9=""),"",D9/C9)</f>
         <v/>
       </c>
-      <c r="M9" s="20" t="str">
+      <c r="M9" s="11" t="str">
         <f aca="false">IF(OR(D9="",D9=0,E9=""),"",E9/D9)</f>
         <v/>
       </c>
-      <c r="N9" s="11" t="str">
+      <c r="N9" s="9" t="str">
         <f aca="false">IF(OR(F9="",F9=0,G9=""),"",G9/F9)</f>
         <v/>
       </c>
-      <c r="O9" s="11" t="str">
+      <c r="O9" s="9" t="str">
         <f aca="false">IF(OR(F9="",F9=0,H9=""),"",(H9+IF(I9="",0,I9))/F9)</f>
         <v/>
       </c>
-      <c r="P9" s="11" t="str">
-        <f aca="false">IF(F9="","",IF(Escenarios!$G$13="COMPLETO",F9*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="20" t="str">
+      <c r="P9" s="9" t="str">
+        <f aca="false">IF(F9="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F9*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="11" t="str">
         <f aca="false">IF(OR(F9="",F9=0,J9=""),"",J9/F9)</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20" t="str">
+      <c r="J10" s="16"/>
+      <c r="K10" s="11" t="str">
         <f aca="false">IF(OR(B10="",B10=0,F10=""),"",F10/B10)</f>
         <v/>
       </c>
-      <c r="L10" s="20" t="str">
+      <c r="L10" s="11" t="str">
         <f aca="false">IF(OR(C10="",C10=0,D10=""),"",D10/C10)</f>
         <v/>
       </c>
-      <c r="M10" s="20" t="str">
+      <c r="M10" s="11" t="str">
         <f aca="false">IF(OR(D10="",D10=0,E10=""),"",E10/D10)</f>
         <v/>
       </c>
-      <c r="N10" s="11" t="str">
+      <c r="N10" s="9" t="str">
         <f aca="false">IF(OR(F10="",F10=0,G10=""),"",G10/F10)</f>
         <v/>
       </c>
-      <c r="O10" s="11" t="str">
+      <c r="O10" s="9" t="str">
         <f aca="false">IF(OR(F10="",F10=0,H10=""),"",(H10+IF(I10="",0,I10))/F10)</f>
         <v/>
       </c>
-      <c r="P10" s="11" t="str">
-        <f aca="false">IF(F10="","",IF(Escenarios!$G$13="COMPLETO",F10*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="20" t="str">
+      <c r="P10" s="9" t="str">
+        <f aca="false">IF(F10="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F10*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="11" t="str">
         <f aca="false">IF(OR(F10="",F10=0,J10=""),"",J10/F10)</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20" t="str">
+      <c r="J11" s="16"/>
+      <c r="K11" s="11" t="str">
         <f aca="false">IF(OR(B11="",B11=0,F11=""),"",F11/B11)</f>
         <v/>
       </c>
-      <c r="L11" s="20" t="str">
+      <c r="L11" s="11" t="str">
         <f aca="false">IF(OR(C11="",C11=0,D11=""),"",D11/C11)</f>
         <v/>
       </c>
-      <c r="M11" s="20" t="str">
+      <c r="M11" s="11" t="str">
         <f aca="false">IF(OR(D11="",D11=0,E11=""),"",E11/D11)</f>
         <v/>
       </c>
-      <c r="N11" s="11" t="str">
+      <c r="N11" s="9" t="str">
         <f aca="false">IF(OR(F11="",F11=0,G11=""),"",G11/F11)</f>
         <v/>
       </c>
-      <c r="O11" s="11" t="str">
+      <c r="O11" s="9" t="str">
         <f aca="false">IF(OR(F11="",F11=0,H11=""),"",(H11+IF(I11="",0,I11))/F11)</f>
         <v/>
       </c>
-      <c r="P11" s="11" t="str">
-        <f aca="false">IF(F11="","",IF(Escenarios!$G$13="COMPLETO",F11*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="20" t="str">
+      <c r="P11" s="9" t="str">
+        <f aca="false">IF(F11="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F11*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="11" t="str">
         <f aca="false">IF(OR(F11="",F11=0,J11=""),"",J11/F11)</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20" t="str">
+      <c r="J12" s="16"/>
+      <c r="K12" s="11" t="str">
         <f aca="false">IF(OR(B12="",B12=0,F12=""),"",F12/B12)</f>
         <v/>
       </c>
-      <c r="L12" s="20" t="str">
+      <c r="L12" s="11" t="str">
         <f aca="false">IF(OR(C12="",C12=0,D12=""),"",D12/C12)</f>
         <v/>
       </c>
-      <c r="M12" s="20" t="str">
+      <c r="M12" s="11" t="str">
         <f aca="false">IF(OR(D12="",D12=0,E12=""),"",E12/D12)</f>
         <v/>
       </c>
-      <c r="N12" s="11" t="str">
+      <c r="N12" s="9" t="str">
         <f aca="false">IF(OR(F12="",F12=0,G12=""),"",G12/F12)</f>
         <v/>
       </c>
-      <c r="O12" s="11" t="str">
+      <c r="O12" s="9" t="str">
         <f aca="false">IF(OR(F12="",F12=0,H12=""),"",(H12+IF(I12="",0,I12))/F12)</f>
         <v/>
       </c>
-      <c r="P12" s="11" t="str">
-        <f aca="false">IF(F12="","",IF(Escenarios!$G$13="COMPLETO",F12*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="20" t="str">
+      <c r="P12" s="9" t="str">
+        <f aca="false">IF(F12="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F12*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="11" t="str">
         <f aca="false">IF(OR(F12="",F12=0,J12=""),"",J12/F12)</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="20" t="str">
+      <c r="J13" s="16"/>
+      <c r="K13" s="11" t="str">
         <f aca="false">IF(OR(B13="",B13=0,F13=""),"",F13/B13)</f>
         <v/>
       </c>
-      <c r="L13" s="20" t="str">
+      <c r="L13" s="11" t="str">
         <f aca="false">IF(OR(C13="",C13=0,D13=""),"",D13/C13)</f>
         <v/>
       </c>
-      <c r="M13" s="20" t="str">
+      <c r="M13" s="11" t="str">
         <f aca="false">IF(OR(D13="",D13=0,E13=""),"",E13/D13)</f>
         <v/>
       </c>
-      <c r="N13" s="11" t="str">
+      <c r="N13" s="9" t="str">
         <f aca="false">IF(OR(F13="",F13=0,G13=""),"",G13/F13)</f>
         <v/>
       </c>
-      <c r="O13" s="11" t="str">
+      <c r="O13" s="9" t="str">
         <f aca="false">IF(OR(F13="",F13=0,H13=""),"",(H13+IF(I13="",0,I13))/F13)</f>
         <v/>
       </c>
-      <c r="P13" s="11" t="str">
-        <f aca="false">IF(F13="","",IF(Escenarios!$G$13="COMPLETO",F13*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="20" t="str">
+      <c r="P13" s="9" t="str">
+        <f aca="false">IF(F13="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F13*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="11" t="str">
         <f aca="false">IF(OR(F13="",F13=0,J13=""),"",J13/F13)</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="20" t="str">
+      <c r="J14" s="16"/>
+      <c r="K14" s="11" t="str">
         <f aca="false">IF(OR(B14="",B14=0,F14=""),"",F14/B14)</f>
         <v/>
       </c>
-      <c r="L14" s="20" t="str">
+      <c r="L14" s="11" t="str">
         <f aca="false">IF(OR(C14="",C14=0,D14=""),"",D14/C14)</f>
         <v/>
       </c>
-      <c r="M14" s="20" t="str">
+      <c r="M14" s="11" t="str">
         <f aca="false">IF(OR(D14="",D14=0,E14=""),"",E14/D14)</f>
         <v/>
       </c>
-      <c r="N14" s="11" t="str">
+      <c r="N14" s="9" t="str">
         <f aca="false">IF(OR(F14="",F14=0,G14=""),"",G14/F14)</f>
         <v/>
       </c>
-      <c r="O14" s="11" t="str">
+      <c r="O14" s="9" t="str">
         <f aca="false">IF(OR(F14="",F14=0,H14=""),"",(H14+IF(I14="",0,I14))/F14)</f>
         <v/>
       </c>
-      <c r="P14" s="11" t="str">
-        <f aca="false">IF(F14="","",IF(Escenarios!$G$13="COMPLETO",F14*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="20" t="str">
+      <c r="P14" s="9" t="str">
+        <f aca="false">IF(F14="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F14*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="11" t="str">
         <f aca="false">IF(OR(F14="",F14=0,J14=""),"",J14/F14)</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="20" t="str">
+      <c r="J15" s="16"/>
+      <c r="K15" s="11" t="str">
         <f aca="false">IF(OR(B15="",B15=0,F15=""),"",F15/B15)</f>
         <v/>
       </c>
-      <c r="L15" s="20" t="str">
+      <c r="L15" s="11" t="str">
         <f aca="false">IF(OR(C15="",C15=0,D15=""),"",D15/C15)</f>
         <v/>
       </c>
-      <c r="M15" s="20" t="str">
+      <c r="M15" s="11" t="str">
         <f aca="false">IF(OR(D15="",D15=0,E15=""),"",E15/D15)</f>
         <v/>
       </c>
-      <c r="N15" s="11" t="str">
+      <c r="N15" s="9" t="str">
         <f aca="false">IF(OR(F15="",F15=0,G15=""),"",G15/F15)</f>
         <v/>
       </c>
-      <c r="O15" s="11" t="str">
+      <c r="O15" s="9" t="str">
         <f aca="false">IF(OR(F15="",F15=0,H15=""),"",(H15+IF(I15="",0,I15))/F15)</f>
         <v/>
       </c>
-      <c r="P15" s="11" t="str">
-        <f aca="false">IF(F15="","",IF(Escenarios!$G$13="COMPLETO",F15*Escenarios!$G$21,"DATOS INCOMPLETOS"))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="20" t="str">
+      <c r="P15" s="9" t="str">
+        <f aca="false">IF(F15="","",IF(ISNUMBER(IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24)),F15*IF(OR($D$2="",'Costes variables'!$B$20&lt;&gt;"COMPLETO"),"DATOS INCOMPLETOS",($D$2-'Costes variables'!$B$15+'Costes variables'!$B$14)*(1-'Costes variables'!$B$25)-'Costes variables'!$B$26-'Costes variables'!$B$24),"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="11" t="str">
         <f aca="false">IF(OR(F15="",F15=0,J15=""),"",J15/F15)</f>
         <v/>
       </c>
@@ -2572,7 +2356,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2607,7 +2391,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -2615,135 +2399,139 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3"/>
-      <c r="C2" s="13" t="n">
-        <f aca="false">IF(Escenarios!G13="COMPLETO",Escenarios!G21,Escenarios!C21)</f>
-        <v>7.04364380165289</v>
-      </c>
-      <c r="D2" s="3" t="str">
-        <f aca="false">IF(Escenarios!G13="COMPLETO","REAL","HIPÓTESIS (Base)")</f>
-        <v>HIPÓTESIS (Base)</v>
-      </c>
-      <c r="E2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="C3" s="12" t="str">
+        <f aca="false">INDEX('Test de precio'!G5:G7,E2)</f>
+        <v>DATOS INCOMPLETOS</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
-        <v>300</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="C5" s="17" t="n">
-        <f aca="false">A5*B5</f>
-        <v>1.5</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <f aca="false">C5*$C$2</f>
-        <v>10.5654657024793</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <f aca="false">C5*'Capital circulante'!$B$6</f>
-        <v>21</v>
-      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <f aca="false">A6*B6</f>
-        <v>10</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <f aca="false">C6*$C$2</f>
-        <v>70.4364380165289</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <f aca="false">C6*'Capital circulante'!$B$6</f>
-        <v>140</v>
-      </c>
+      <c r="A6" s="16"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="17" t="str">
+        <f aca="false">IF(OR(A6="",B6=""),"",A6*B6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="9" t="str">
+        <f aca="false">IF(C6="","",IF(ISNUMBER($C$3),C6*$C$3,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="E6" s="9" t="str">
+        <f aca="false">IF(C6="","",IF(ISNUMBER('Costes variables'!$B$27),C6*'Costes variables'!$B$27,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
-        <v>3000</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <f aca="false">A7*B7</f>
-        <v>30</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <f aca="false">C7*$C$2</f>
-        <v>211.309314049587</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <f aca="false">C7*'Capital circulante'!$B$6</f>
-        <v>420</v>
-      </c>
+      <c r="A7" s="16"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="17" t="str">
+        <f aca="false">IF(OR(A7="",B7=""),"",A7*B7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="9" t="str">
+        <f aca="false">IF(C7="","",IF(ISNUMBER($C$3),C7*$C$3,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="E7" s="9" t="str">
+        <f aca="false">IF(C7="","",IF(ISNUMBER('Costes variables'!$B$27),C7*'Costes variables'!$B$27,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
-        <v>10000</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <f aca="false">A8*B8</f>
-        <v>150</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <f aca="false">C8*$C$2</f>
-        <v>1056.54657024793</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <f aca="false">C8*'Capital circulante'!$B$6</f>
-        <v>2100</v>
-      </c>
+      <c r="A8" s="16"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="17" t="str">
+        <f aca="false">IF(OR(A8="",B8=""),"",A8*B8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="9" t="str">
+        <f aca="false">IF(C8="","",IF(ISNUMBER($C$3),C8*$C$3,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="E8" s="9" t="str">
+        <f aca="false">IF(C8="","",IF(ISNUMBER('Costes variables'!$B$27),C8*'Costes variables'!$B$27,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="17" t="str">
+        <f aca="false">IF(OR(A9="",B9=""),"",A9*B9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="9" t="str">
+        <f aca="false">IF(C9="","",IF(ISNUMBER($C$3),C9*$C$3,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="E9" s="9" t="str">
+        <f aca="false">IF(C9="","",IF(ISNUMBER('Costes variables'!$B$27),C9*'Costes variables'!$B$27,"DATOS INCOMPLETOS"))</f>
+        <v/>
+      </c>
+      <c r="F9" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/05_ECONOMIA_UNITARIA.xlsx
+++ b/docs/05_ECONOMIA_UNITARIA.xlsx
@@ -500,7 +500,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Economía unitaria · VINCIRENA (marca provisional) · Mercado EE. UU. · USD · V2.2 (14/10/2026)</t>
+          <t>Economía unitaria · SILEXORA · Mercado EE. UU. · USD · V2.2 (14/10/2026)</t>
         </is>
       </c>
     </row>
